--- a/MANO_DE_OBRA_importar.xlsx
+++ b/MANO_DE_OBRA_importar.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -116,7 +116,7 @@
     <definedName name="ACARQ">#REF!</definedName>
     <definedName name="AMB" localSheetId="0">#REF!</definedName>
     <definedName name="AMB">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANO DE OBRA (2)'!$A$1:$O$28627</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANO DE OBRA (2)'!$A$1:$N$28624</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="AS" localSheetId="0">[4]LOTE1!#REF!</definedName>
     <definedName name="AS">[4]LOTE1!#REF!</definedName>
@@ -396,26 +396,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="241">
   <si>
     <t>Código</t>
   </si>
@@ -771,294 +757,6 @@
     <t>Categoría</t>
   </si>
   <si>
-    <t>Pintor empapelador---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Fierrero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Carpintero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Encofrador o carpintero de ribera---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Plomero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Electricista o instalador de revestimiento en general---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Ayudante de perforador---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Cadenero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Mampostero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Enlucidor---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Hojalatero---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Técnico liniero eléctrico---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Técnico en montaje de subestaciones---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Técnico electromecánico de construcción---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Obrero especializado en la elaboración de prefabricados de hormigón---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Parqueteros y colocadores de pisos---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Operador de perforador (En Construcción)---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Perfilero (En Construcción)---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Técnico albañilería---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Técnico obras civiles---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Maestro de Obra---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Maestro eléctrico/liniero/subestaciones---ESTRUCTURA OCUPACIONAL C1</t>
-  </si>
-  <si>
-    <t>Maestro mayor en ejecución de obras civiles---ESTRUCTURA OCUPACIONAL C1</t>
-  </si>
-  <si>
-    <t>Maestro soldador especializado (En Construcción- Estr,Oc,C1)---ESTRUCTURA OCUPACIONAL C1</t>
-  </si>
-  <si>
-    <t>Inspector de obra---ESTRUCTURA OCUPACIONAL B3</t>
-  </si>
-  <si>
-    <t>Supervisor eléctrico general / Supervisor sanitario general---ESTRUCTURA OCUPACIONAL B3</t>
-  </si>
-  <si>
-    <t>Ingeniero eléctrico---ESTRUCTURA OCUPACIONAL B1</t>
-  </si>
-  <si>
-    <t>Ingeniero civil (Estructural, Hidráulico y Vial)---ESTRUCTURA OCUPACIONAL B1</t>
-  </si>
-  <si>
-    <t>Residente de Obra---ESTRUCTURA OCUPACIONAL B1</t>
-  </si>
-  <si>
-    <t>Laboratorista (En Construcción- Estr, Oc, C1)---LABORATORIO</t>
-  </si>
-  <si>
-    <t>Topógrafo (En Construcción- Estr,Oc,C1)---TOPOGRAFÍA</t>
-  </si>
-  <si>
-    <t>Dibujante (En Construcción- Estr,Oc,C2)---DIBUJANTES</t>
-  </si>
-  <si>
-    <t>Motoniveladora---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Grúa puente de elevación---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Pala de castillo---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Grúa estacionaria---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Draga/Dragline---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Tractor carriles o ruedas (bulldozer, topador, roturador, malacate, traílla)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Tractor tiende tubos (side bone)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Mototrailla---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Cargadora frontal (Payloader sobre ruedas u orugas)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Retroexcavadora---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Auto-tren cama baja (trailer)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Fresadora de pavimento asfáltico/Rotomil---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Recicladora de pavimento asfáltico/Rotomil---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Planta de emulsión asfáltica---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Máquina para sellos asfálticos---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Squider---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Camión articulado con volteo (En Construcción)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Camión mezclador para micropavimentos---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Camión cisterna para cemento y asfalto (Adicional al traslado debe conectar los equipos para embarque y desembarque, monitorear equipo de presión)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Perforadora de brazos múltiples (jumbo)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Máquina tuneladora (topo)---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Concretera rodante/mixer---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Máquina extendedora de adoquín---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Máquina zanjadora---ESTRUCTURA OCUPACIONAL C1 (GRUPO I)</t>
-  </si>
-  <si>
-    <t>Operador responsable de la planta hormigonera---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador responsable de la planta asfáltica---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de track drill---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de rodillo autopropulsado---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de distribuidor de asfalto---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de distribuidor de agregados---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de acabadora de pavimento de hormigón---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de acabadora de pavimento asfáltico---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de grada elevadora / canastilla elevadora---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de bomba impulsadora de hormigón, equipos móviles de planta, molino de amianto, planta dosificadora de hormigón, productos terminados (tanques moldeados, postes de alumbrado eléctrico, acabados de piezas afines)---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de tractor de ruedas (barredora, cegadora, rodillo remolcado, franjeadora)---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de caldero planta asfáltica---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de barredora autopropulsada---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de punzón neumático---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador compresor---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Camión de carga frontal (En Construcción)---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador de camión de volteo con o sin articulación/Dumper (En Construcción)---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador mini excavadora/mini cargadora con sus aditamentos---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Operador termoformado---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Técnico en carpintería---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Técnico en mantenimiento de viviendas y edificios---ESTRUCTURA OCUPACIONAL C2 (GRUPO II)</t>
-  </si>
-  <si>
-    <t>Engrasador o abastecedor responsable en construcción (En Construcción-  Estr,Oc,D2)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Para camiones pesados y extra pesados con o sin remolque de más de 3,5 toneladas (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Tráiler (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Volquetas (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Tanqueros (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Plataformas (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Otros camiones (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Para ferrocarriles (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Para auto ferros (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Camiones para transportar mercancías o sustancias peligrosas y otros vehículos especiales (Estr, Oc, C1)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Para transporte Escolares-Personal y turismo hasta 45 pasajeros ( Estr, Oc, C2)---ESTRUCTURA OCUPACIONAL C1 (Estr,Oc,C1) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>CHOFER: Para camiones sin acoplados (Estr, Oc, C3)---ESTRUCTURA OCUPACIONAL C3 (Estr,Oc,C3) CHOFERES SECCION C: SIN TÍTULO</t>
-  </si>
-  <si>
-    <t>Operador de bomba lanzadora de concreto---ESTRUCTURA OCUPACIONAL C2</t>
-  </si>
-  <si>
-    <t>Preparador de mezcla de materias primas---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Tubero (En Construcción)---ESTRUCTURA OCUPACIONAL D2</t>
-  </si>
-  <si>
-    <t>Resanador en general (En Construcción)---ESTRUCTURA OCUPACIONAL E2</t>
-  </si>
-  <si>
-    <t>Tinero de pasta de amianto---ESTRUCTURA OCUPACIONAL E2</t>
-  </si>
-  <si>
-    <t>Excavadora Grúa (Grupo A: operadores tabla 1)---ESTRUCTURA OCUPACIONAL C2 (GRUPO A)</t>
-  </si>
-  <si>
-    <t>Perforadora de pozos profundos o rodantes (Grupo A: operadores tabla 1)---ESTRUCTURA OCUPACIONAL C2 (GRUPO A)</t>
-  </si>
-  <si>
     <t>Tarifa Hora</t>
   </si>
   <si>
@@ -1066,6 +764,366 @@
   </si>
   <si>
     <t>Término</t>
+  </si>
+  <si>
+    <t>Peón</t>
+  </si>
+  <si>
+    <t>Ayudante de Albañil</t>
+  </si>
+  <si>
+    <t>Ayudante de Carpintero</t>
+  </si>
+  <si>
+    <t>Ayudante de Electricista</t>
+  </si>
+  <si>
+    <t>Albañil</t>
+  </si>
+  <si>
+    <t>Operador de equipo liviano</t>
+  </si>
+  <si>
+    <t>Pintor</t>
+  </si>
+  <si>
+    <t>Pintor de exteriores</t>
+  </si>
+  <si>
+    <t>Excavadora</t>
+  </si>
+  <si>
+    <t>Operador responsable de la planta trituradora</t>
+  </si>
+  <si>
+    <t>ESTRUCTURA OCUPACIONAL E2 (PRIMERA Y SEGUNDA CATEGORÍA)</t>
+  </si>
+  <si>
+    <t>200001Peón</t>
+  </si>
+  <si>
+    <t>200002Ayudante de Albañil</t>
+  </si>
+  <si>
+    <t>200003Ayudante de Carpintero</t>
+  </si>
+  <si>
+    <t>200004Ayudante de Electricista</t>
+  </si>
+  <si>
+    <t>200005Albañil</t>
+  </si>
+  <si>
+    <t>200006Operador de equipo liviano</t>
+  </si>
+  <si>
+    <t>200007Pintor</t>
+  </si>
+  <si>
+    <t>200008Pintor de exteriores</t>
+  </si>
+  <si>
+    <t>200009Pintor empapelador</t>
+  </si>
+  <si>
+    <t>200010Fierrero</t>
+  </si>
+  <si>
+    <t>200011Carpintero</t>
+  </si>
+  <si>
+    <t>200012Encofrador o carpintero de ribera</t>
+  </si>
+  <si>
+    <t>200013Plomero</t>
+  </si>
+  <si>
+    <t>200014Electricista o instalador de revestimiento en general</t>
+  </si>
+  <si>
+    <t>200015Ayudante de perforador</t>
+  </si>
+  <si>
+    <t>200016Cadenero</t>
+  </si>
+  <si>
+    <t>200017Mampostero</t>
+  </si>
+  <si>
+    <t>200018Enlucidor</t>
+  </si>
+  <si>
+    <t>200019Hojalatero</t>
+  </si>
+  <si>
+    <t>200020Técnico liniero eléctrico</t>
+  </si>
+  <si>
+    <t>200021Técnico en montaje de subestaciones</t>
+  </si>
+  <si>
+    <t>200022Técnico electromecánico de construcción</t>
+  </si>
+  <si>
+    <t>200023Obrero especializado en la elaboración de prefabricados de hormigón</t>
+  </si>
+  <si>
+    <t>200024Parqueteros y colocadores de pisos</t>
+  </si>
+  <si>
+    <t>200025Operador de perforador (En Construcción)</t>
+  </si>
+  <si>
+    <t>200026Perfilero (En Construcción)</t>
+  </si>
+  <si>
+    <t>200027Técnico albañilería</t>
+  </si>
+  <si>
+    <t>200028Técnico obras civiles</t>
+  </si>
+  <si>
+    <t>200029Maestro de Obra</t>
+  </si>
+  <si>
+    <t>200030Maestro eléctrico/liniero/subestaciones</t>
+  </si>
+  <si>
+    <t>200031Maestro mayor en ejecución de obras civiles</t>
+  </si>
+  <si>
+    <t>200032Maestro soldador especializado (En Construcción- Estr,Oc,C1)</t>
+  </si>
+  <si>
+    <t>200033Maestro soldador especializado (En Construcción- Estr,Oc,C1)</t>
+  </si>
+  <si>
+    <t>200034Inspector de obra</t>
+  </si>
+  <si>
+    <t>200035Supervisor eléctrico general / Supervisor sanitario general</t>
+  </si>
+  <si>
+    <t>200036Ingeniero eléctrico</t>
+  </si>
+  <si>
+    <t>200037Ingeniero civil (Estructural, Hidráulico y Vial)</t>
+  </si>
+  <si>
+    <t>200038Residente de Obra</t>
+  </si>
+  <si>
+    <t>200039Laboratorista (En Construcción- Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>200040Topógrafo (En Construcción- Estr,Oc,C1)</t>
+  </si>
+  <si>
+    <t>200041Dibujante (En Construcción- Estr,Oc,C2)</t>
+  </si>
+  <si>
+    <t>407001Motoniveladora</t>
+  </si>
+  <si>
+    <t>407001Excavadora</t>
+  </si>
+  <si>
+    <t>407002Grúa puente de elevación</t>
+  </si>
+  <si>
+    <t>407003Pala de castillo</t>
+  </si>
+  <si>
+    <t>407004Grúa estacionaria</t>
+  </si>
+  <si>
+    <t>407005Draga/Dragline</t>
+  </si>
+  <si>
+    <t>407006Tractor carriles o ruedas (bulldozer, topador, roturador, malacate, traílla)</t>
+  </si>
+  <si>
+    <t>407007Tractor tiende tubos (side bone)</t>
+  </si>
+  <si>
+    <t>407008Mototrailla</t>
+  </si>
+  <si>
+    <t>407009Cargadora frontal (Payloader sobre ruedas u orugas)</t>
+  </si>
+  <si>
+    <t>407010Retroexcavadora</t>
+  </si>
+  <si>
+    <t>407011Auto-tren cama baja (trailer)</t>
+  </si>
+  <si>
+    <t>407012Fresadora de pavimento asfáltico/Rotomil</t>
+  </si>
+  <si>
+    <t>407013Recicladora de pavimento asfáltico/Rotomil</t>
+  </si>
+  <si>
+    <t>407014Planta de emulsión asfáltica</t>
+  </si>
+  <si>
+    <t>407015Máquina para sellos asfálticos</t>
+  </si>
+  <si>
+    <t>407016Squider</t>
+  </si>
+  <si>
+    <t>407017Camión articulado con volteo (En Construcción)</t>
+  </si>
+  <si>
+    <t>407018Camión mezclador para micropavimentos</t>
+  </si>
+  <si>
+    <t>407019Camión cisterna para cemento y asfalto (Adicional al traslado debe conectar los equipos para embarque y desembarque, monitorear equipo de presión)</t>
+  </si>
+  <si>
+    <t>407020Camión cisterna para cemento y asfalto (Adicional al traslado debe conectar los equipos para embarque y desembarque, monitorear equipo de presión)</t>
+  </si>
+  <si>
+    <t>407021Perforadora de brazos múltiples (jumbo)</t>
+  </si>
+  <si>
+    <t>407022Máquina tuneladora (topo)</t>
+  </si>
+  <si>
+    <t>407023Concretera rodante/mixer</t>
+  </si>
+  <si>
+    <t>407024Máquina extendedora de adoquín</t>
+  </si>
+  <si>
+    <t>407025Máquina zanjadora</t>
+  </si>
+  <si>
+    <t>407101Operador responsable de la planta hormigonera</t>
+  </si>
+  <si>
+    <t>407101Operador responsable de la planta trituradora</t>
+  </si>
+  <si>
+    <t>407102Operador responsable de la planta asfáltica</t>
+  </si>
+  <si>
+    <t>407103Operador de track drill</t>
+  </si>
+  <si>
+    <t>407104Operador de rodillo autopropulsado</t>
+  </si>
+  <si>
+    <t>417105Operador de distribuidor de asfalto</t>
+  </si>
+  <si>
+    <t>417106Operador de distribuidor de agregados</t>
+  </si>
+  <si>
+    <t>417107Operador de acabadora de pavimento de hormigón</t>
+  </si>
+  <si>
+    <t>417108Operador de acabadora de pavimento asfáltico</t>
+  </si>
+  <si>
+    <t>417109Operador de grada elevadora / canastilla elevadora</t>
+  </si>
+  <si>
+    <t>417110Operador de bomba impulsadora de hormigón, equipos móviles de planta, molino de amianto, planta dosificadora de hormigón, productos terminados (tanques moldeados, postes de alumbrado eléctrico, acabados de piezas afines)</t>
+  </si>
+  <si>
+    <t>417111Operador de tractor de ruedas (barredora, cegadora, rodillo remolcado, franjeadora)</t>
+  </si>
+  <si>
+    <t>417112Operador de caldero planta asfáltica</t>
+  </si>
+  <si>
+    <t>417113Operador de barredora autopropulsada</t>
+  </si>
+  <si>
+    <t>417114Operador de punzón neumático</t>
+  </si>
+  <si>
+    <t>417115Operador compresor</t>
+  </si>
+  <si>
+    <t>417116Camión de carga frontal (En Construcción)</t>
+  </si>
+  <si>
+    <t>417117Operador de camión de volteo con o sin articulación/Dumper (En Construcción)</t>
+  </si>
+  <si>
+    <t>417118Operador mini excavadora/mini cargadora con sus aditamentos</t>
+  </si>
+  <si>
+    <t>417119Operador termoformado</t>
+  </si>
+  <si>
+    <t>417120Técnico en carpintería</t>
+  </si>
+  <si>
+    <t>417121Técnico en mantenimiento de viviendas y edificios</t>
+  </si>
+  <si>
+    <t>420001Engrasador o abastecedor responsable en construcción (En Construcción-  Estr,Oc,D2)</t>
+  </si>
+  <si>
+    <t>420002CHOFER: Para camiones pesados y extra pesados con o sin remolque de más de 3,5 toneladas (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>420003CHOFER: Tráiler (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>420004CHOFER: Volquetas (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>420005CHOFER: Tanqueros (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>420006CHOFER: Plataformas (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>430001CHOFER: Otros camiones (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>430002CHOFER: Para ferrocarriles (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>430003CHOFER: Para auto ferros (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>430004CHOFER: Camiones para transportar mercancías o sustancias peligrosas y otros vehículos especiales (Estr, Oc, C1)</t>
+  </si>
+  <si>
+    <t>440001CHOFER: Para transporte Escolares-Personal y turismo hasta 45 pasajeros ( Estr, Oc, C2)</t>
+  </si>
+  <si>
+    <t>440002CHOFER: Para camiones sin acoplados (Estr, Oc, C3)</t>
+  </si>
+  <si>
+    <t>450001Operador de bomba lanzadora de concreto</t>
+  </si>
+  <si>
+    <t>460001Preparador de mezcla de materias primas</t>
+  </si>
+  <si>
+    <t>460002Tubero (En Construcción)</t>
+  </si>
+  <si>
+    <t>470001Resanador en general (En Construcción)</t>
+  </si>
+  <si>
+    <t>470002Tinero de pasta de amianto</t>
+  </si>
+  <si>
+    <t>450002Excavadora Grúa (Grupo A: operadores tabla 1)</t>
+  </si>
+  <si>
+    <t>450003Perforadora de pozos profundos o rodantes (Grupo A: operadores tabla 1)</t>
+  </si>
+  <si>
+    <t>450004Perforadora de pozos profundos o rodantes (Grupo A: operadores tabla 1)</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1224,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1174,17 +1232,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1198,14 +1251,53 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="2" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda 2" xfId="7"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="4"/>
     <cellStyle name="Normal 2 2 3" xfId="3"/>
@@ -1233,8 +1325,9 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1247,8 +1340,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1267,8 +1358,9 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1281,8 +1373,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1302,7 +1392,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1315,8 +1405,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -29621,8 +29709,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TABLA_M_O32" displayName="TABLA_M_O32" ref="A1:H100" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Normal" dataCellStyle="Normal">
-  <autoFilter ref="A1:H100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TABLA_M_O32" displayName="TABLA_M_O32" ref="A1:H110" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7" headerRowCellStyle="Normal" dataCellStyle="Normal">
+  <autoFilter ref="A1:H110"/>
   <tableColumns count="8">
     <tableColumn id="4" name="Código" dataDxfId="6" dataCellStyle="Normal 2"/>
     <tableColumn id="8" name="Nombre" dataDxfId="5" dataCellStyle="Normal 2"/>
@@ -29900,2612 +29988,2873 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="32.88671875" customWidth="1"/>
     <col min="3" max="3" width="44.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="22"/>
     <col min="8" max="8" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H1" s="10" t="s">
+      <c r="E1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>200009</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="A2" s="10">
+        <v>200001</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F2" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="12">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F2" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>118</v>
+      <c r="H2" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>200010</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="A3" s="10">
+        <v>200002</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F3" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="12">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F3" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>119</v>
+      <c r="H3" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>200011</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="A4" s="10">
+        <v>200003</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F4" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="E4" s="12">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F4" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>120</v>
+      <c r="H4" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>200012</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="A5" s="10">
+        <v>200004</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F5" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="E5" s="12">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F5" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>121</v>
+      <c r="H5" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>200013</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="10">
+        <v>200005</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="12">
         <v>4.28</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="20">
         <v>34.24</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>122</v>
+      <c r="H6" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>200014</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="10">
+        <v>200006</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="12">
         <v>4.28</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="20">
         <v>34.24</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>123</v>
+      <c r="H7" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>200015</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="10">
+        <v>200007</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="12">
         <v>4.28</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="20">
         <v>34.24</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>124</v>
+      <c r="H8" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>200016</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="10">
+        <v>200008</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="12">
         <v>4.28</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="20">
         <v>34.24</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>125</v>
+      <c r="H9" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
-        <v>200017</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="10">
+        <v>200009</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="12">
         <v>4.28</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="20">
         <v>34.24</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>126</v>
+      <c r="H10" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
-        <v>200018</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="10">
+        <v>200010</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="12">
         <v>4.28</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="20">
         <v>34.24</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>127</v>
+      <c r="H11" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>200019</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="10">
+        <v>200011</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="12">
         <v>4.28</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="20">
         <v>34.24</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>128</v>
+      <c r="H12" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
-        <v>200020</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="A13" s="10">
+        <v>200012</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="12">
         <v>4.28</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="20">
         <v>34.24</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>129</v>
+      <c r="H13" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
-        <v>200021</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="A14" s="10">
+        <v>200013</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="12">
         <v>4.28</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="20">
         <v>34.24</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>130</v>
+      <c r="H14" s="6" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
-        <v>200022</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="A15" s="10">
+        <v>200014</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="12">
         <v>4.28</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="20">
         <v>34.24</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>131</v>
+      <c r="H15" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
-        <v>200023</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="10">
+        <v>200015</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="12">
         <v>4.28</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="20">
         <v>34.24</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>132</v>
+      <c r="H16" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
-        <v>200024</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="A17" s="10">
+        <v>200016</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="12">
         <v>4.28</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="20">
         <v>34.24</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>133</v>
+      <c r="H17" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
-        <v>200025</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="A18" s="10">
+        <v>200017</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="12">
         <v>4.28</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="20">
         <v>34.24</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>134</v>
+      <c r="H18" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
-        <v>200026</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="A19" s="10">
+        <v>200018</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="12">
         <v>4.28</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="20">
         <v>34.24</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>135</v>
+      <c r="H19" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
-        <v>200027</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="A20" s="10">
+        <v>200019</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="12">
         <v>4.28</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="20">
         <v>34.24</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>136</v>
+      <c r="H20" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
-        <v>200028</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="A21" s="10">
+        <v>200020</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="12">
         <v>4.28</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="20">
         <v>34.24</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>137</v>
+      <c r="H21" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
-        <v>200029</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="A22" s="10">
+        <v>200021</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="12">
         <v>4.28</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="20">
         <v>34.24</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>138</v>
+      <c r="H22" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <v>200030</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="A23" s="10">
+        <v>200022</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="12">
         <v>4.28</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="20">
         <v>34.24</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>139</v>
+      <c r="H23" s="6" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
-        <v>200031</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="A24" s="10">
+        <v>200023</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="12">
         <v>4.28</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="20">
         <v>34.24</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>140</v>
+      <c r="H24" s="6" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
-        <v>200032</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="A25" s="10">
+        <v>200024</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="12">
         <v>4.28</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="20">
         <v>34.24</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>141</v>
+      <c r="H25" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
-        <v>200033</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="A26" s="10">
+        <v>200025</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E26" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F26" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="E26" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F26" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>141</v>
+      <c r="H26" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
-        <v>200034</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="A27" s="10">
+        <v>200026</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F27" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G27" s="6" t="s">
+      <c r="E27" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F27" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>142</v>
+      <c r="H27" s="6" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
-        <v>200035</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="A28" s="10">
+        <v>200027</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F28" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="E28" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F28" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>143</v>
+      <c r="H28" s="6" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
-        <v>200036</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="A29" s="10">
+        <v>200028</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F29" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="E29" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F29" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>144</v>
+      <c r="H29" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
-        <v>200037</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="A30" s="10">
+        <v>200029</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F30" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="E30" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F30" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>145</v>
+      <c r="H30" s="6" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
-        <v>200038</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="A31" s="10">
+        <v>200030</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F31" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G31" s="6" t="s">
+      <c r="E31" s="14">
+        <v>4.75</v>
+      </c>
+      <c r="F31" s="20">
+        <v>38</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>146</v>
+      <c r="H31" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
-        <v>200039</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="A32" s="10">
+        <v>200031</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="F32" s="20">
         <v>38</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F32" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>147</v>
+      <c r="H32" s="6" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
-        <v>200040</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="A33" s="10">
+        <v>200032</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F33" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G33" s="6" t="s">
+      <c r="E33" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="F33" s="20">
+        <v>38</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>148</v>
+      <c r="H33" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
-        <v>200041</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="A34" s="10">
+        <v>200033</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F34" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="E34" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="F34" s="20">
+        <v>38</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>149</v>
+      <c r="H34" s="6" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
-        <v>407001</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="A35" s="10">
+        <v>200034</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F35" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="E35" s="12">
+        <v>4.76</v>
+      </c>
+      <c r="F35" s="20">
+        <v>38.08</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>150</v>
+      <c r="H35" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
-        <v>407002</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="A36" s="10">
+        <v>200035</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F36" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="E36" s="12">
+        <v>4.76</v>
+      </c>
+      <c r="F36" s="20">
+        <v>38.08</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>151</v>
+      <c r="H36" s="6" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
-        <v>407003</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="A37" s="10">
+        <v>200036</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F37" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="E37" s="12">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F37" s="20">
+        <v>38.159999999999997</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H37" s="9" t="s">
-        <v>152</v>
+      <c r="H37" s="6" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
-        <v>407004</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="A38" s="10">
+        <v>200037</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F38" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="E38" s="12">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F38" s="20">
+        <v>38.159999999999997</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H38" s="9" t="s">
-        <v>153</v>
+      <c r="H38" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
-        <v>407005</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="A39" s="10">
+        <v>200038</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F39" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G39" s="6" t="s">
+      <c r="E39" s="12">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F39" s="20">
+        <v>38.159999999999997</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H39" s="9" t="s">
-        <v>154</v>
+      <c r="H39" s="6" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
-        <v>407006</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="A40" s="10">
+        <v>200039</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F40" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="E40" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="F40" s="20">
+        <v>38</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>155</v>
+      <c r="H40" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
-        <v>407007</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="A41" s="10">
+        <v>200040</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F41" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G41" s="6" t="s">
+      <c r="E41" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="F41" s="20">
+        <v>38</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>156</v>
+      <c r="H41" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
-        <v>407008</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="A42" s="10">
+        <v>200041</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F42" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="E42" s="12">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F42" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>157</v>
+      <c r="H42" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
-        <v>407009</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="A43" s="3">
+        <v>407000</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F43" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G43" s="6" t="s">
+      <c r="E43" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F43" s="20">
+        <v>38</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>158</v>
+      <c r="H43" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
-        <v>407010</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="A44" s="5">
+        <v>407001</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F44" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="E44" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F44" s="20">
+        <v>38</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="9" t="s">
-        <v>159</v>
+      <c r="H44" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
-        <v>407011</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="A45" s="3">
+        <v>407002</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F45" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G45" s="6" t="s">
+      <c r="E45" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F45" s="20">
+        <v>38</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="9" t="s">
-        <v>160</v>
+      <c r="H45" s="6" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
-        <v>407012</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="A46" s="5">
+        <v>407003</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F46" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="E46" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F46" s="20">
+        <v>38</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H46" s="9" t="s">
-        <v>161</v>
+      <c r="H46" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
-        <v>407013</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="A47" s="3">
+        <v>407004</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F47" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G47" s="6" t="s">
+      <c r="E47" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F47" s="20">
+        <v>38</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H47" s="9" t="s">
-        <v>162</v>
+      <c r="H47" s="6" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>407014</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="A48" s="5">
+        <v>407005</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E48" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F48" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="E48" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F48" s="20">
+        <v>38</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H48" s="9" t="s">
-        <v>163</v>
+      <c r="H48" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
-        <v>407015</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="A49" s="3">
+        <v>407006</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E49" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F49" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="E49" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F49" s="20">
+        <v>38</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="9" t="s">
-        <v>164</v>
+      <c r="H49" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
-        <v>407016</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="A50" s="5">
+        <v>407007</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E50" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F50" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="E50" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F50" s="20">
+        <v>38</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H50" s="9" t="s">
-        <v>165</v>
+      <c r="H50" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
-        <v>407017</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="A51" s="3">
+        <v>407008</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E51" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F51" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G51" s="6" t="s">
+      <c r="E51" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F51" s="20">
+        <v>38</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H51" s="9" t="s">
-        <v>166</v>
+      <c r="H51" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
-        <v>407018</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="A52" s="5">
+        <v>407009</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E52" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F52" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="E52" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F52" s="20">
+        <v>38</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="9" t="s">
-        <v>167</v>
+      <c r="H52" s="6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
-        <v>407019</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="A53" s="3">
+        <v>407010</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E53" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F53" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G53" s="6" t="s">
+      <c r="E53" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F53" s="20">
+        <v>38</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H53" s="9" t="s">
-        <v>168</v>
+      <c r="H53" s="6" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>407020</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="A54" s="5">
+        <v>407011</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E54" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F54" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="E54" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F54" s="20">
+        <v>38</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H54" s="9" t="s">
-        <v>168</v>
+      <c r="H54" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
-        <v>407021</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="A55" s="3">
+        <v>407012</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E55" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F55" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G55" s="6" t="s">
+      <c r="E55" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F55" s="20">
+        <v>38</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H55" s="9" t="s">
-        <v>169</v>
+      <c r="H55" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
-        <v>407022</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="A56" s="5">
+        <v>407013</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E56" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F56" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="E56" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F56" s="20">
+        <v>38</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H56" s="9" t="s">
-        <v>170</v>
+      <c r="H56" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
-        <v>407023</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="A57" s="3">
+        <v>407014</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E57" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F57" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G57" s="6" t="s">
+      <c r="E57" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F57" s="20">
+        <v>38</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>171</v>
+      <c r="H57" s="6" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
-        <v>407024</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="A58" s="5">
+        <v>407015</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E58" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F58" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="E58" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F58" s="20">
+        <v>38</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="9" t="s">
-        <v>172</v>
+      <c r="H58" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
-        <v>407025</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="A59" s="3">
+        <v>407016</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E59" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F59" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G59" s="6" t="s">
+      <c r="E59" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F59" s="20">
+        <v>38</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="9" t="s">
-        <v>173</v>
+      <c r="H59" s="6" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5">
-        <v>407101</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="A60" s="3">
+        <v>407017</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E60" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F60" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="E60" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F60" s="20">
+        <v>38</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H60" s="9" t="s">
-        <v>174</v>
+      <c r="H60" s="6" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5">
-        <v>407102</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="A61" s="3">
+        <v>407018</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E61" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F61" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G61" s="6" t="s">
+      <c r="E61" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F61" s="20">
+        <v>38</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H61" s="9" t="s">
-        <v>175</v>
+      <c r="H61" s="6" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
-        <v>407103</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="A62" s="5">
+        <v>407019</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E62" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F62" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="E62" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F62" s="20">
+        <v>38</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="9" t="s">
-        <v>176</v>
+      <c r="H62" s="6" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5">
-        <v>407104</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="A63" s="3">
+        <v>407020</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E63" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F63" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G63" s="6" t="s">
+      <c r="E63" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F63" s="20">
+        <v>38</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H63" s="9" t="s">
-        <v>177</v>
+      <c r="H63" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7">
-        <v>417105</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="A64" s="5">
+        <v>407021</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E64" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F64" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="E64" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F64" s="20">
+        <v>38</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H64" s="9" t="s">
-        <v>178</v>
+      <c r="H64" s="6" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
-        <v>417106</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="A65" s="3">
+        <v>407022</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E65" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F65" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G65" s="6" t="s">
+      <c r="E65" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F65" s="20">
+        <v>38</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H65" s="9" t="s">
-        <v>179</v>
+      <c r="H65" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7">
-        <v>417107</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" s="4" t="s">
+      <c r="A66" s="5">
+        <v>407023</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E66" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F66" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="E66" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F66" s="20">
+        <v>38</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H66" s="9" t="s">
-        <v>180</v>
+      <c r="H66" s="6" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5">
-        <v>417108</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D67" s="4" t="s">
+      <c r="A67" s="3">
+        <v>407024</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E67" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F67" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G67" s="6" t="s">
+      <c r="E67" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F67" s="20">
+        <v>38</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H67" s="9" t="s">
-        <v>181</v>
+      <c r="H67" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7">
-        <v>417109</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D68" s="4" t="s">
+      <c r="A68" s="5">
+        <v>407025</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E68" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F68" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="E68" s="20">
+        <v>4.75</v>
+      </c>
+      <c r="F68" s="20">
+        <v>38</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H68" s="9" t="s">
-        <v>182</v>
+      <c r="H68" s="6" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5">
-        <v>417110</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="A69" s="3">
+        <v>407100</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E69" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F69" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G69" s="6" t="s">
+      <c r="E69" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F69" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H69" s="9" t="s">
-        <v>183</v>
+      <c r="H69" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7">
-        <v>417111</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" s="3" t="s">
+      <c r="A70" s="5">
+        <v>407101</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E70" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F70" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G70" s="6" t="s">
+      <c r="E70" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F70" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="9" t="s">
-        <v>184</v>
+      <c r="H70" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5">
-        <v>417112</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="A71" s="3">
+        <v>407102</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E71" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F71" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G71" s="6" t="s">
+      <c r="E71" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F71" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H71" s="9" t="s">
-        <v>185</v>
+      <c r="H71" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7">
-        <v>417113</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="A72" s="5">
+        <v>407103</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E72" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F72" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="E72" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F72" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H72" s="9" t="s">
-        <v>186</v>
+      <c r="H72" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5">
-        <v>417114</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="A73" s="3">
+        <v>407104</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E73" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F73" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G73" s="6" t="s">
+      <c r="E73" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F73" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H73" s="9" t="s">
-        <v>187</v>
+      <c r="H73" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7">
-        <v>417115</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="A74" s="5">
+        <v>417105</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E74" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F74" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="E74" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F74" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H74" s="9" t="s">
-        <v>188</v>
+      <c r="H74" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5">
-        <v>417116</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="A75" s="3">
+        <v>417106</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E75" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F75" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G75" s="6" t="s">
+      <c r="E75" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F75" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H75" s="9" t="s">
-        <v>189</v>
+      <c r="H75" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="7">
-        <v>417117</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="A76" s="5">
+        <v>417107</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E76" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F76" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G76" s="6" t="s">
+      <c r="E76" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F76" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H76" s="9" t="s">
-        <v>190</v>
+      <c r="H76" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="5">
-        <v>417118</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="A77" s="3">
+        <v>417108</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E77" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F77" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G77" s="6" t="s">
+      <c r="E77" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F77" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H77" s="9" t="s">
-        <v>191</v>
+      <c r="H77" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7">
-        <v>417119</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="A78" s="5">
+        <v>417109</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E78" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F78" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="E78" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F78" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H78" s="9" t="s">
-        <v>192</v>
+      <c r="H78" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5">
-        <v>417120</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="A79" s="3">
+        <v>417110</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F79" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G79" s="6" t="s">
+      <c r="E79" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F79" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H79" s="9" t="s">
-        <v>193</v>
+      <c r="H79" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="7">
-        <v>417121</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="A80" s="5">
+        <v>417111</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E80" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F80" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G80" s="6" t="s">
+      <c r="E80" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F80" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H80" s="9" t="s">
-        <v>194</v>
+      <c r="H80" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="7">
-        <v>420001</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81" s="4" t="s">
+      <c r="A81" s="5">
+        <v>417112</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E81" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F81" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G81" s="6" t="s">
+      <c r="E81" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F81" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H81" s="9" t="s">
-        <v>195</v>
+      <c r="H81" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5">
-        <v>420002</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="A82" s="3">
+        <v>417113</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E82" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F82" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G82" s="6" t="s">
+      <c r="E82" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F82" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H82" s="9" t="s">
-        <v>196</v>
+      <c r="H82" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="7">
-        <v>420003</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="A83" s="5">
+        <v>417114</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E83" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F83" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G83" s="6" t="s">
+      <c r="E83" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F83" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="9" t="s">
-        <v>197</v>
+      <c r="H83" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5">
-        <v>420004</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="A84" s="3">
+        <v>417115</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E84" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F84" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G84" s="6" t="s">
+      <c r="E84" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F84" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H84" s="9" t="s">
-        <v>198</v>
+      <c r="H84" s="6" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="7">
-        <v>420005</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="A85" s="5">
+        <v>417116</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E85" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F85" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G85" s="6" t="s">
+      <c r="E85" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F85" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H85" s="9" t="s">
-        <v>199</v>
+      <c r="H85" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5">
-        <v>420006</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="A86" s="3">
+        <v>417117</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E86" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F86" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G86" s="6" t="s">
+      <c r="E86" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F86" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H86" s="9" t="s">
-        <v>200</v>
+      <c r="H86" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5">
-        <v>430001</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="A87" s="3">
+        <v>417118</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E87" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F87" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G87" s="6" t="s">
+      <c r="E87" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F87" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H87" s="9" t="s">
-        <v>201</v>
+      <c r="H87" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="7">
-        <v>430002</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="A88" s="5">
+        <v>417119</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E88" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F88" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="E88" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F88" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H88" s="9" t="s">
-        <v>202</v>
+      <c r="H88" s="6" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5">
-        <v>430003</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="A89" s="3">
+        <v>417120</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E89" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F89" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G89" s="6" t="s">
+      <c r="E89" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F89" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H89" s="9" t="s">
-        <v>203</v>
+      <c r="H89" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="7">
-        <v>430004</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="A90" s="5">
+        <v>417121</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E90" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F90" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G90" s="6" t="s">
+      <c r="E90" s="20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F90" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H90" s="9" t="s">
-        <v>204</v>
+      <c r="H90" s="6" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5">
-        <v>440001</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D91" s="4" t="s">
+      <c r="A91" s="3">
+        <v>420001</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="20">
         <v>4.28</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="20">
         <v>34.24</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="9" t="s">
-        <v>205</v>
+      <c r="H91" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="7">
-        <v>440002</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="A92" s="5">
+        <v>420002</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E92" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F92" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="E92" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F92" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H92" s="9" t="s">
-        <v>206</v>
+      <c r="H92" s="6" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="7">
-        <v>450001</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="A93" s="5">
+        <v>420003</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E93" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F93" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G93" s="6" t="s">
+      <c r="E93" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F93" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H93" s="9" t="s">
-        <v>207</v>
+      <c r="H93" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="7">
-        <v>460001</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="A94" s="5">
+        <v>420004</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E94" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F94" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="E94" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F94" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="9" t="s">
-        <v>208</v>
+      <c r="H94" s="6" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5">
-        <v>460002</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="A95" s="3">
+        <v>420005</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E95" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F95" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G95" s="6" t="s">
+      <c r="E95" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F95" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H95" s="9" t="s">
-        <v>209</v>
+      <c r="H95" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5">
-        <v>470001</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="A96" s="3">
+        <v>420006</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E96" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F96" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G96" s="6" t="s">
+      <c r="E96" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F96" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H96" s="9" t="s">
-        <v>210</v>
+      <c r="H96" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="7">
-        <v>470002</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97" s="4" t="s">
+      <c r="A97" s="5">
+        <v>430001</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E97" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F97" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G97" s="6" t="s">
+      <c r="E97" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F97" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H97" s="9" t="s">
-        <v>211</v>
+      <c r="H97" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="7">
-        <v>450002</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="A98" s="5">
+        <v>430002</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E98" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F98" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G98" s="6" t="s">
+      <c r="E98" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F98" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H98" s="9" t="s">
-        <v>212</v>
+      <c r="H98" s="6" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
-        <v>450003</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D99" s="4" t="s">
+      <c r="A99" s="3">
+        <v>430003</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E99" s="3">
-        <v>4.28</v>
-      </c>
-      <c r="F99" s="3">
-        <v>34.24</v>
-      </c>
-      <c r="G99" s="6" t="s">
+      <c r="E99" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F99" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H99" s="9" t="s">
-        <v>213</v>
+      <c r="H99" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="7">
+      <c r="A100" s="5">
+        <v>430004</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E100" s="20">
+        <v>6.22</v>
+      </c>
+      <c r="F100" s="20">
+        <v>49.76</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A101" s="9">
+        <v>440001</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E101" s="13">
+        <v>6.15</v>
+      </c>
+      <c r="F101" s="20">
+        <v>49.2</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A102" s="9">
+        <v>440002</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E102" s="13">
+        <v>6.01</v>
+      </c>
+      <c r="F102" s="20">
+        <v>48.08</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A103" s="9">
+        <v>450001</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E103" s="13">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F103" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A104" s="9">
+        <v>460001</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E104" s="13">
+        <v>4.28</v>
+      </c>
+      <c r="F104" s="20">
+        <v>34.24</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="9">
+        <v>460002</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E105" s="13">
+        <v>4.28</v>
+      </c>
+      <c r="F105" s="20">
+        <v>34.24</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A106" s="9">
+        <v>470001</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E106" s="13">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F106" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="9">
+        <v>470002</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E107" s="13">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F107" s="20">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A108" s="9">
+        <v>450002</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E108" s="13">
+        <v>4.28</v>
+      </c>
+      <c r="F108" s="20">
+        <v>34.24</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A109" s="9">
+        <v>450003</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E109" s="13">
+        <v>4.28</v>
+      </c>
+      <c r="F109" s="20">
+        <v>34.24</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A110" s="9">
         <v>450004</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B110" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C110" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D110" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E110" s="13">
         <v>4.28</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F110" s="20">
         <v>34.24</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G110" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="9" t="s">
-        <v>213</v>
+      <c r="H110" s="11" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
